--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486382_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486382_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.4223</v>
+        <v>7.1545</v>
       </c>
       <c r="E2" t="n">
-        <v>5.2164</v>
+        <v>5.8869</v>
       </c>
       <c r="F2" t="n">
-        <v>1.2059</v>
+        <v>1.2676</v>
       </c>
       <c r="G2" t="n">
         <v>5.6277</v>
@@ -610,13 +610,13 @@
         <v>1.9576</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.163</v>
+        <v>-0.4308</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.8904</v>
+        <v>-0.2199</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.2726</v>
+        <v>-0.2109</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.0595</v>
+        <v>4.4506</v>
       </c>
       <c r="E3" t="n">
-        <v>3.4606</v>
+        <v>2.79</v>
       </c>
       <c r="F3" t="n">
-        <v>1.5989</v>
+        <v>1.6605</v>
       </c>
       <c r="G3" t="n">
         <v>4.2341</v>
@@ -688,13 +688,13 @@
         <v>1.0875</v>
       </c>
       <c r="S3" t="n">
-        <v>1.1527</v>
+        <v>0.5438</v>
       </c>
       <c r="T3" t="n">
-        <v>0.5312</v>
+        <v>-0.1394</v>
       </c>
       <c r="U3" t="n">
-        <v>0.6215000000000001</v>
+        <v>0.6832</v>
       </c>
       <c r="V3" t="n">
         <v>0.7602</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>X. OROZ URIA</t>
+          <t>M. KAMBA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.2594</v>
+        <v>2.8318</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.9867</v>
+        <v>0.1483</v>
       </c>
       <c r="F4" t="n">
-        <v>3.246</v>
+        <v>2.6835</v>
       </c>
       <c r="G4" t="n">
-        <v>1.156</v>
+        <v>1.5002</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9002</v>
+        <v>0.9304</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2558</v>
+        <v>0.5698</v>
       </c>
       <c r="J4" t="n">
-        <v>0.3832</v>
+        <v>0.5003</v>
       </c>
       <c r="K4" t="n">
-        <v>1.6821</v>
+        <v>0.7847</v>
       </c>
       <c r="L4" t="n">
-        <v>-1.2989</v>
+        <v>-0.2844</v>
       </c>
       <c r="M4" t="n">
-        <v>0.7728</v>
+        <v>0.9999</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.7819</v>
+        <v>0.1457</v>
       </c>
       <c r="O4" t="n">
-        <v>1.5546</v>
+        <v>0.8542</v>
       </c>
       <c r="P4" t="n">
-        <v>0.6525</v>
+        <v>0.435</v>
       </c>
       <c r="Q4" t="n">
         <v>-1.0875</v>
       </c>
       <c r="R4" t="n">
-        <v>1.7401</v>
+        <v>1.5225</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3769</v>
+        <v>-0.1328</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.2824</v>
+        <v>-0.2199</v>
       </c>
       <c r="U4" t="n">
-        <v>0.6592</v>
+        <v>0.0871</v>
       </c>
       <c r="V4" t="n">
-        <v>0.074</v>
+        <v>1.0294</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>0.9554</v>
       </c>
       <c r="X4" t="n">
         <v>0.074</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. KAMBA</t>
+          <t>X. OROZ URIA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.0996</v>
+        <v>2.7796</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.5223</v>
+        <v>-0.6514</v>
       </c>
       <c r="F5" t="n">
-        <v>2.6219</v>
+        <v>3.431</v>
       </c>
       <c r="G5" t="n">
-        <v>1.5002</v>
+        <v>1.156</v>
       </c>
       <c r="H5" t="n">
-        <v>0.9304</v>
+        <v>0.9002</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5698</v>
+        <v>0.2558</v>
       </c>
       <c r="J5" t="n">
-        <v>0.5003</v>
+        <v>0.3832</v>
       </c>
       <c r="K5" t="n">
-        <v>0.7847</v>
+        <v>1.6821</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.2844</v>
+        <v>-1.2989</v>
       </c>
       <c r="M5" t="n">
-        <v>0.9999</v>
+        <v>0.7728</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1457</v>
+        <v>-0.7819</v>
       </c>
       <c r="O5" t="n">
-        <v>0.8542</v>
+        <v>1.5546</v>
       </c>
       <c r="P5" t="n">
-        <v>0.435</v>
+        <v>0.6525</v>
       </c>
       <c r="Q5" t="n">
         <v>-1.0875</v>
       </c>
       <c r="R5" t="n">
-        <v>1.5225</v>
+        <v>1.7401</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.865</v>
+        <v>0.8971</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.8904</v>
+        <v>0.0529</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0255</v>
+        <v>0.8442</v>
       </c>
       <c r="V5" t="n">
-        <v>1.0294</v>
+        <v>0.074</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9554</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
         <v>0.074</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.8367</v>
+        <v>1.8021</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.8269</v>
+        <v>-0.4916</v>
       </c>
       <c r="F6" t="n">
-        <v>2.6636</v>
+        <v>2.2937</v>
       </c>
       <c r="G6" t="n">
         <v>0.6327</v>
@@ -922,13 +922,13 @@
         <v>1.305</v>
       </c>
       <c r="S6" t="n">
-        <v>0.8494</v>
+        <v>0.8147</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.2139</v>
+        <v>0.1214</v>
       </c>
       <c r="U6" t="n">
-        <v>1.0632</v>
+        <v>0.6934</v>
       </c>
       <c r="V6" t="n">
         <v>1.2246</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.3882</v>
+        <v>1.2879</v>
       </c>
       <c r="E7" t="n">
-        <v>4.0081</v>
+        <v>3.7846</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.62</v>
+        <v>-2.4967</v>
       </c>
       <c r="G7" t="n">
         <v>1.9477</v>
@@ -1000,13 +1000,13 @@
         <v>1.7401</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.7999000000000001</v>
+        <v>-0.9001</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.0769</v>
+        <v>-0.3004</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.723</v>
+        <v>-0.5997</v>
       </c>
       <c r="V7" t="n">
         <v>-1.4997</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. WINTERING</t>
+          <t>O. GOMEZ FERNANDEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.3133</v>
+        <v>-0.5093</v>
       </c>
       <c r="E8" t="n">
-        <v>0.555</v>
+        <v>-0.7953</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.8683</v>
+        <v>0.286</v>
       </c>
       <c r="G8" t="n">
-        <v>0.9113</v>
+        <v>-0.5778</v>
       </c>
       <c r="H8" t="n">
-        <v>1.2532</v>
+        <v>0.0182</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.3419</v>
+        <v>-0.596</v>
       </c>
       <c r="J8" t="n">
-        <v>2.533</v>
+        <v>-0.7268</v>
       </c>
       <c r="K8" t="n">
-        <v>1.156</v>
+        <v>0.0182</v>
       </c>
       <c r="L8" t="n">
-        <v>1.377</v>
+        <v>-0.7451</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.6217</v>
+        <v>0.149</v>
       </c>
       <c r="N8" t="n">
-        <v>0.09710000000000001</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.7188</v>
+        <v>0.149</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.6525</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.1751</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.5225</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.1816</v>
+        <v>0.06850000000000001</v>
       </c>
       <c r="T8" t="n">
-        <v>0.1971</v>
+        <v>-0.06850000000000001</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.3787</v>
+        <v>0.137</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.3904</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.3904</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>O. GOMEZ FERNANDEZ</t>
+          <t>A. WINTERING</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.386</v>
+        <v>-0.7911</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.7953</v>
+        <v>0.108</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4093</v>
+        <v>-0.8991</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.5778</v>
+        <v>0.9113</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0182</v>
+        <v>1.2532</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.596</v>
+        <v>-0.3419</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.7268</v>
+        <v>2.533</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0182</v>
+        <v>1.156</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.7451</v>
+        <v>1.377</v>
       </c>
       <c r="M9" t="n">
-        <v>0.149</v>
+        <v>-1.6217</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>0.09710000000000001</v>
       </c>
       <c r="O9" t="n">
-        <v>0.149</v>
+        <v>-1.7188</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>-0.6525</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-2.1751</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.5225</v>
       </c>
       <c r="S9" t="n">
-        <v>0.1918</v>
+        <v>-0.6594</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.06850000000000001</v>
+        <v>-0.2499</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2603</v>
+        <v>-0.4095</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-0.3904</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-0.3904</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.6257</v>
+        <v>-1.4927</v>
       </c>
       <c r="E10" t="n">
-        <v>1.5206</v>
+        <v>0.9618</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.1463</v>
+        <v>-2.4545</v>
       </c>
       <c r="G10" t="n">
         <v>-0.5755</v>
@@ -1234,13 +1234,13 @@
         <v>1.7401</v>
       </c>
       <c r="S10" t="n">
-        <v>0.7655</v>
+        <v>-0.1015</v>
       </c>
       <c r="T10" t="n">
-        <v>0.9421</v>
+        <v>0.3833</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1767</v>
+        <v>-0.4849</v>
       </c>
       <c r="V10" t="n">
         <v>-2.5558</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.202</v>
+        <v>-1.9747</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.3899</v>
+        <v>-1.5016</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.8121</v>
+        <v>-0.4731</v>
       </c>
       <c r="G11" t="n">
         <v>0.5512</v>
@@ -1312,13 +1312,13 @@
         <v>1.5225</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.8495</v>
+        <v>-0.6222</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.0769</v>
+        <v>-0.1887</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.7726</v>
+        <v>-0.4335</v>
       </c>
       <c r="V11" t="n">
         <v>-1.2512</v>
@@ -1348,7 +1348,7 @@
         <v>15.5387</v>
       </c>
       <c r="E12" t="n">
-        <v>10.2396</v>
+        <v>10.2397</v>
       </c>
       <c r="F12" t="n">
         <v>5.298900000000001</v>
@@ -1393,10 +1393,10 @@
         <v>-0.5227000000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.8289999999999998</v>
+        <v>-0.8291000000000001</v>
       </c>
       <c r="U12" t="n">
-        <v>0.3061</v>
+        <v>0.3064000000000001</v>
       </c>
       <c r="V12" t="n">
         <v>-2.6089</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>2.0669</v>
+        <v>2.4252</v>
       </c>
       <c r="E13" t="n">
-        <v>2.8671</v>
+        <v>2.9788</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.8002</v>
+        <v>-0.5536</v>
       </c>
       <c r="G13" t="n">
         <v>1.469</v>
@@ -1468,13 +1468,13 @@
         <v>0.87</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.9111</v>
+        <v>-0.5528</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.4795</v>
+        <v>-0.3677</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.4317</v>
+        <v>-0.1851</v>
       </c>
       <c r="V13" t="n">
         <v>0.6389</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.6183</v>
+        <v>1.2176</v>
       </c>
       <c r="E14" t="n">
         <v>1.572</v>
       </c>
       <c r="F14" t="n">
-        <v>0.0463</v>
+        <v>-0.3544</v>
       </c>
       <c r="G14" t="n">
         <v>3.1593</v>
@@ -1546,13 +1546,13 @@
         <v>0.87</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.6373</v>
+        <v>-1.038</v>
       </c>
       <c r="T14" t="n">
         <v>-0.8904</v>
       </c>
       <c r="U14" t="n">
-        <v>0.2532</v>
+        <v>-0.1475</v>
       </c>
       <c r="V14" t="n">
         <v>-0.6863</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. PARRADO CALABRIA</t>
+          <t>R. VILA SOLEY</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.3756</v>
+        <v>0.3276</v>
       </c>
       <c r="E15" t="n">
-        <v>0.5377</v>
+        <v>2.3709</v>
       </c>
       <c r="F15" t="n">
-        <v>0.8379</v>
+        <v>-2.0434</v>
       </c>
       <c r="G15" t="n">
-        <v>-2.0781</v>
+        <v>1.2151</v>
       </c>
       <c r="H15" t="n">
-        <v>-3.6583</v>
+        <v>-0.3834</v>
       </c>
       <c r="I15" t="n">
-        <v>1.5802</v>
+        <v>1.5985</v>
       </c>
       <c r="J15" t="n">
-        <v>0.1716</v>
+        <v>3.3804</v>
       </c>
       <c r="K15" t="n">
-        <v>-1.9154</v>
+        <v>0.9125</v>
       </c>
       <c r="L15" t="n">
-        <v>2.087</v>
+        <v>2.4679</v>
       </c>
       <c r="M15" t="n">
-        <v>-2.2497</v>
+        <v>-2.1652</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.7429</v>
+        <v>-1.2959</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.5068</v>
+        <v>-0.8694</v>
       </c>
       <c r="P15" t="n">
-        <v>-1.5225</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>-3.2626</v>
+        <v>-1.0875</v>
       </c>
       <c r="R15" t="n">
-        <v>1.7401</v>
+        <v>1.0875</v>
       </c>
       <c r="S15" t="n">
-        <v>3.1067</v>
+        <v>0.2424</v>
       </c>
       <c r="T15" t="n">
-        <v>1.3687</v>
+        <v>0.0781</v>
       </c>
       <c r="U15" t="n">
-        <v>1.738</v>
+        <v>0.1643</v>
       </c>
       <c r="V15" t="n">
-        <v>1.8695</v>
+        <v>-1.13</v>
       </c>
       <c r="W15" t="n">
-        <v>2.2599</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.3904</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. ALONSO CUEVAS</t>
+          <t>A. PARRADO CALABRIA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.1401</v>
+        <v>-0.0155</v>
       </c>
       <c r="E16" t="n">
-        <v>1.6306</v>
+        <v>-0.0211</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.7707</v>
+        <v>0.0057</v>
       </c>
       <c r="G16" t="n">
-        <v>-4.2062</v>
+        <v>-2.0781</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.4539</v>
+        <v>-3.6583</v>
       </c>
       <c r="I16" t="n">
-        <v>-2.7523</v>
+        <v>1.5802</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.7469</v>
+        <v>0.1716</v>
       </c>
       <c r="K16" t="n">
-        <v>0.073</v>
+        <v>-1.9154</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.8199</v>
+        <v>2.087</v>
       </c>
       <c r="M16" t="n">
-        <v>-3.4593</v>
+        <v>-2.2497</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.5269</v>
+        <v>-1.7429</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.9324</v>
+        <v>-0.5068</v>
       </c>
       <c r="P16" t="n">
-        <v>0.2175</v>
+        <v>-1.5225</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.0875</v>
+        <v>-3.2626</v>
       </c>
       <c r="R16" t="n">
-        <v>1.305</v>
+        <v>1.7401</v>
       </c>
       <c r="S16" t="n">
-        <v>3.6534</v>
+        <v>1.7157</v>
       </c>
       <c r="T16" t="n">
-        <v>3.2698</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="U16" t="n">
-        <v>0.3836</v>
+        <v>0.9058</v>
       </c>
       <c r="V16" t="n">
-        <v>0.1952</v>
+        <v>1.8695</v>
       </c>
       <c r="W16" t="n">
-        <v>0.1952</v>
+        <v>2.2599</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-0.3904</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>R. VILA SOLEY</t>
+          <t>F. TERINS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,40 +1735,40 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.1733</v>
+        <v>-0.2675</v>
       </c>
       <c r="E17" t="n">
-        <v>2.1474</v>
+        <v>0.2062</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.3208</v>
+        <v>-0.4736</v>
       </c>
       <c r="G17" t="n">
-        <v>1.2151</v>
+        <v>-0.0237</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.3834</v>
+        <v>-0.6389</v>
       </c>
       <c r="I17" t="n">
-        <v>1.5985</v>
+        <v>0.6152</v>
       </c>
       <c r="J17" t="n">
-        <v>3.3804</v>
+        <v>1.1471</v>
       </c>
       <c r="K17" t="n">
-        <v>0.9125</v>
+        <v>0.1095</v>
       </c>
       <c r="L17" t="n">
-        <v>2.4679</v>
+        <v>1.0376</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.1652</v>
+        <v>-1.1707</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.2959</v>
+        <v>-0.7484</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.8694</v>
+        <v>-0.4224</v>
       </c>
       <c r="P17" t="n">
         <v>0</v>
@@ -1780,28 +1780,28 @@
         <v>1.0875</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.2585</v>
+        <v>0.3212</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.1454</v>
+        <v>0.1466</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1131</v>
+        <v>0.1745</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.13</v>
+        <v>-0.5649999999999999</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.13</v>
+        <v>-0.5649999999999999</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>F. TERINS</t>
+          <t>A. ALONSO CUEVAS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.3369</v>
+        <v>-1.8666</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.0174</v>
+        <v>-0.1575</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.3195</v>
+        <v>-1.709</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.0237</v>
+        <v>-4.2062</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.6389</v>
+        <v>-1.4539</v>
       </c>
       <c r="I18" t="n">
-        <v>0.6152</v>
+        <v>-2.7523</v>
       </c>
       <c r="J18" t="n">
-        <v>1.1471</v>
+        <v>-0.7469</v>
       </c>
       <c r="K18" t="n">
-        <v>0.1095</v>
+        <v>0.073</v>
       </c>
       <c r="L18" t="n">
-        <v>1.0376</v>
+        <v>-0.8199</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.1707</v>
+        <v>-3.4593</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.7484</v>
+        <v>-1.5269</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.4224</v>
+        <v>-1.9324</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>0.2175</v>
       </c>
       <c r="Q18" t="n">
         <v>-1.0875</v>
       </c>
       <c r="R18" t="n">
-        <v>1.0875</v>
+        <v>1.305</v>
       </c>
       <c r="S18" t="n">
-        <v>0.2518</v>
+        <v>1.9269</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.0769</v>
+        <v>1.4817</v>
       </c>
       <c r="U18" t="n">
-        <v>0.3287</v>
+        <v>0.4452</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.5649999999999999</v>
+        <v>0.1952</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>0.1952</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.5649999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.609</v>
+        <v>-1.9655</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.2131</v>
+        <v>-0.8779</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.3958</v>
+        <v>-1.0876</v>
       </c>
       <c r="G19" t="n">
         <v>-0.7869</v>
@@ -1936,13 +1936,13 @@
         <v>0.87</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.156</v>
+        <v>-0.5125</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.4675</v>
+        <v>-0.1322</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.6886</v>
+        <v>-0.3803</v>
       </c>
       <c r="V19" t="n">
         <v>0.6389</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>G. JOFRESA SARRET</t>
+          <t>M. JACKSON</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.9851</v>
+        <v>-3.0046</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.4086</v>
+        <v>-1.8876</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.5765</v>
+        <v>-1.1171</v>
       </c>
       <c r="G20" t="n">
-        <v>-4.3066</v>
+        <v>-3.7683</v>
       </c>
       <c r="H20" t="n">
-        <v>-2.6276</v>
+        <v>-4.6138</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.679</v>
+        <v>0.8455</v>
       </c>
       <c r="J20" t="n">
-        <v>-2.5573</v>
+        <v>-1.0531</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.0672</v>
+        <v>-2.1074</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.4901</v>
+        <v>1.0543</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.7493</v>
+        <v>-2.7151</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.5604</v>
+        <v>-2.5063</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.1889</v>
+        <v>-0.2088</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.6525</v>
+        <v>0.87</v>
       </c>
       <c r="Q20" t="n">
         <v>-1.0875</v>
       </c>
       <c r="R20" t="n">
-        <v>0.435</v>
+        <v>1.9576</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.5256999999999999</v>
+        <v>-0.5501</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.5239</v>
+        <v>-0.5071</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0018</v>
+        <v>-0.043</v>
       </c>
       <c r="V20" t="n">
-        <v>1.4997</v>
+        <v>0.4437</v>
       </c>
       <c r="W20" t="n">
         <v>0.7602</v>
       </c>
       <c r="X20" t="n">
-        <v>0.7395</v>
+        <v>-0.3165</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>M. JACKSON</t>
+          <t>G. JOFRESA SARRET</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.0027</v>
+        <v>-3.4957</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.6699</v>
+        <v>-3.0733</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.3328</v>
+        <v>-0.4224</v>
       </c>
       <c r="G21" t="n">
-        <v>-3.7683</v>
+        <v>-4.3066</v>
       </c>
       <c r="H21" t="n">
-        <v>-4.6138</v>
+        <v>-2.6276</v>
       </c>
       <c r="I21" t="n">
-        <v>0.8455</v>
+        <v>-1.679</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.0531</v>
+        <v>-2.5573</v>
       </c>
       <c r="K21" t="n">
-        <v>-2.1074</v>
+        <v>-1.0672</v>
       </c>
       <c r="L21" t="n">
-        <v>1.0543</v>
+        <v>-1.4901</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.7151</v>
+        <v>-1.7493</v>
       </c>
       <c r="N21" t="n">
-        <v>-2.5063</v>
+        <v>-1.5604</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.2088</v>
+        <v>-0.1889</v>
       </c>
       <c r="P21" t="n">
-        <v>0.87</v>
+        <v>-0.6525</v>
       </c>
       <c r="Q21" t="n">
         <v>-1.0875</v>
       </c>
       <c r="R21" t="n">
-        <v>1.9576</v>
+        <v>0.435</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.5481</v>
+        <v>-0.0363</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.2894</v>
+        <v>-0.1887</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2587</v>
+        <v>0.1523</v>
       </c>
       <c r="V21" t="n">
-        <v>0.4437</v>
+        <v>1.4997</v>
       </c>
       <c r="W21" t="n">
         <v>0.7602</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.3165</v>
+        <v>0.7395</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.3465</v>
+        <v>-4.1037</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.8039</v>
+        <v>-3.4686</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.5426</v>
+        <v>-0.635</v>
       </c>
       <c r="G22" t="n">
         <v>-2.1542</v>
@@ -2170,13 +2170,13 @@
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.0172</v>
+        <v>0.2256</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.1935</v>
+        <v>0.1418</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1763</v>
+        <v>0.0838</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.0058</v>
+        <v>-4.79</v>
       </c>
       <c r="E23" t="n">
         <v>-2.9409</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.0649</v>
+        <v>-1.8492</v>
       </c>
       <c r="G23" t="n">
         <v>-3.9273</v>
@@ -2248,13 +2248,13 @@
         <v>0.6525</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.4352</v>
+        <v>-1.2194</v>
       </c>
       <c r="T23" t="n">
         <v>-0.8784</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.5568</v>
+        <v>-0.341</v>
       </c>
       <c r="V23" t="n">
         <v>-0.2958</v>
@@ -2281,7 +2281,7 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-15.5386</v>
+        <v>-15.5387</v>
       </c>
       <c r="E24" t="n">
         <v>-5.298999999999999</v>
@@ -2296,13 +2296,13 @@
         <v>-14.3401</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.0676</v>
+        <v>-1.067600000000001</v>
       </c>
       <c r="J24" t="n">
-        <v>2.519499999999999</v>
+        <v>2.519500000000002</v>
       </c>
       <c r="K24" t="n">
-        <v>0.8537000000000001</v>
+        <v>0.8537000000000003</v>
       </c>
       <c r="L24" t="n">
         <v>1.6658</v>
@@ -2326,13 +2326,13 @@
         <v>10.8752</v>
       </c>
       <c r="S24" t="n">
-        <v>0.5227999999999997</v>
+        <v>0.5226999999999999</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.3063999999999992</v>
+        <v>-0.3062999999999997</v>
       </c>
       <c r="U24" t="n">
-        <v>0.8290999999999999</v>
+        <v>0.829</v>
       </c>
       <c r="V24" t="n">
         <v>2.6088</v>
